--- a/media/broadcast_list.xlsx
+++ b/media/broadcast_list.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Name</t>
   </si>
@@ -45,6 +45,18 @@
   </si>
   <si>
     <t>+91 9014828318</t>
+  </si>
+  <si>
+    <t>Achyuth</t>
+  </si>
+  <si>
+    <t>+91 9177219347</t>
+  </si>
+  <si>
+    <t>Karunakar Reddy</t>
+  </si>
+  <si>
+    <t>+91 9000666914</t>
   </si>
 </sst>
 </file>
@@ -1206,8 +1218,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="2"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
@@ -1228,19 +1240,39 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="1"/>
       <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
